--- a/classifykatdpnew/kan_gat_dp_epsilon_controlled_history long time ep2.5.xlsx
+++ b/classifykatdpnew/kan_gat_dp_epsilon_controlled_history long time ep2.5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\flight delay\stpn paper\STPN-main\classifykatdpnew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6620F6-8571-4370-A2A7-D27103C29B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3493990-DC82-4602-B8DD-7A234CCA5E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="106">
   <si>
     <t>delta</t>
   </si>
@@ -302,6 +302,42 @@
   </si>
   <si>
     <t>run1</t>
+  </si>
+  <si>
+    <t>Loaded DP model from: kan_gat_dp_proper.pth</t>
+  </si>
+  <si>
+    <t>Final ε: 2.787</t>
+  </si>
+  <si>
+    <t>Final δ: 1.00e-05</t>
+  </si>
+  <si>
+    <t>TEST RESULTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Precision: 0.9786 | Recall: 0.6013 | F1: 0.7449 | Accuracy: 0.7632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  MAE: 2.7182 min | RMSE: 3.4970 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3-step Arrival  -&gt; MAE: 4.7505, RMSE: 5.7294, R²: -0.5848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3-step Departure-&gt; MAE: 1.5018, RMSE: 1.8852, R²: 0.7255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  6-step Arrival  -&gt; MAE: 4.9290, RMSE: 5.8242, R²: -0.6368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  6-step Departure-&gt; MAE: 1.6725, RMSE: 2.0843, R²: 0.6646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  12-step Arrival  -&gt; MAE: 5.3722, RMSE: 6.2151, R²: -0.8619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  12-step Departure-&gt; MAE: 2.2023, RMSE: 2.7473, R²: 0.4173</t>
   </si>
 </sst>
 </file>
@@ -2178,136 +2214,189 @@
       </c>
     </row>
     <row r="48" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
+        <v>94</v>
+      </c>
       <c r="V48" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E50" t="s">
+        <v>96</v>
+      </c>
       <c r="V50" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V51" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E52" t="s">
+        <v>51</v>
+      </c>
       <c r="V52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E53" t="s">
+        <v>97</v>
+      </c>
       <c r="V53" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E54" t="s">
+        <v>51</v>
+      </c>
       <c r="V54" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="55" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V55" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="56" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
       <c r="V56" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="57" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E57" t="s">
+        <v>98</v>
+      </c>
       <c r="V57" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V58" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="59" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
       <c r="V59" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E60" t="s">
+        <v>99</v>
+      </c>
       <c r="V60" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V61" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E62" t="s">
+        <v>16</v>
+      </c>
       <c r="V62" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="63" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E63" t="s">
+        <v>100</v>
+      </c>
       <c r="V63" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="64" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E64" t="s">
+        <v>101</v>
+      </c>
       <c r="V64" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E65" t="s">
+        <v>102</v>
+      </c>
       <c r="V65" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="66" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E66" t="s">
+        <v>103</v>
+      </c>
       <c r="V66" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E67" t="s">
+        <v>104</v>
+      </c>
       <c r="V67" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="5:22" x14ac:dyDescent="0.3">
+      <c r="E68" t="s">
+        <v>105</v>
+      </c>
       <c r="V68" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V69" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="70" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V70" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V71" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="72" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V72" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="73" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V73" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="74" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V74" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="75" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:22" x14ac:dyDescent="0.3">
       <c r="V75" t="s">
         <v>91</v>
       </c>
